--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightAllocationExport.xlsx
@@ -160,7 +160,7 @@
     <t>{.fromWarehouseName}</t>
   </si>
   <si>
-    <t>{.createTime}</t>
+    <t>{.createTimeStr}</t>
   </si>
 </sst>
 </file>
